--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G2">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G5">

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G2">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5">

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU6"/>
+  <dimension ref="A1:AU7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1392,6 +1392,169 @@
       <c r="AU6" t="inlineStr">
         <is>
           <t>2026-09-24 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Amal Tiznit</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ittihad Tanger</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>-1</v>
+      </c>
+      <c r="AN7">
+        <v>-1</v>
+      </c>
+      <c r="AO7">
+        <v>-1</v>
+      </c>
+      <c r="AP7">
+        <v>-1</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G4">

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O6">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="S6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T6">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="U6">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
         <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>3.68</v>
+        <v>3.99</v>
       </c>
       <c r="AA6">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AB6">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="AD6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="O6">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P6">
         <v>2.6</v>
@@ -1305,10 +1305,10 @@
         <v>1.32</v>
       </c>
       <c r="T6">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="U6">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="V6">
         <v>1.46</v>
@@ -1317,13 +1317,13 @@
         <v>1.09</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>3.99</v>
+        <v>3.72</v>
       </c>
       <c r="AA6">
         <v>1.77</v>
@@ -1360,7 +1360,7 @@
         <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="O6">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="Q6">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="R6">
         <v>2.04</v>
@@ -1305,10 +1305,10 @@
         <v>1.32</v>
       </c>
       <c r="T6">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
         <v>1.46</v>
@@ -1317,7 +1317,7 @@
         <v>1.09</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
         <v>1.2</v>
@@ -1326,19 +1326,19 @@
         <v>3.72</v>
       </c>
       <c r="AA6">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB6">
         <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
         <v>1.57</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AK6">
         <v>1.4</v>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="O6">
         <v>3.1</v>
@@ -1296,55 +1296,55 @@
         <v>2.53</v>
       </c>
       <c r="Q6">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="R6">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="S6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="V6">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z6">
-        <v>3.72</v>
+        <v>3.34</v>
       </c>
       <c r="AA6">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AB6">
         <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="AD6">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AE6">
         <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q7">
         <v>0</v>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="Q6">
         <v>3.32</v>
       </c>
       <c r="R6">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
         <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.98</v>
+        <v>2.77</v>
       </c>
       <c r="U6">
         <v>2.58</v>
@@ -1320,22 +1320,22 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z6">
         <v>3.34</v>
       </c>
       <c r="AA6">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AB6">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AC6">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AD6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
         <v>1.1</v>
@@ -1344,7 +1344,7 @@
         <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK6">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="R3">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S3">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="V3">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z3">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA3">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC3">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="AD3">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AG3">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>2.07</v>
+        <v>1.39</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q5">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="R5">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="S5">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T5">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="U5">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z5">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB5">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC5">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="AD5">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AG5">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>1.39</v>
+        <v>2.07</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q3">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="R3">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="S3">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="T3">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="U3">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z3">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="AA3">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB3">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AC3">
-        <v>2.81</v>
+        <v>2.41</v>
       </c>
       <c r="AD3">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AG3">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK3">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.85</v>
+        <v>1.69</v>
       </c>
       <c r="O4">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P4">
-        <v>1.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q4">
-        <v>4.25</v>
+        <v>2.1</v>
       </c>
       <c r="R4">
         <v>2.4</v>
       </c>
       <c r="S4">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="T4">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U4">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V4">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W4">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
         <v>4.5</v>
       </c>
       <c r="AA4">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB4">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AC4">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="AD4">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AE4">
         <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AG4">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK4">
-        <v>1.2</v>
+        <v>2.07</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="R5">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S5">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="V5">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA5">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="AD5">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AG5">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>2.07</v>
+        <v>1.39</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O7">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P7">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC7">
         <v>0</v>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O2">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Q2">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="R2">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="S2">
         <v>1.28</v>
@@ -656,43 +656,43 @@
         <v>3.08</v>
       </c>
       <c r="U2">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W2">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z2">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="AA2">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB2">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AC2">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE2">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG2">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK2">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -801,61 +801,61 @@
         <v>3.85</v>
       </c>
       <c r="O3">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P3">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q3">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="R3">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="T3">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="U3">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA3">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AB3">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="AC3">
-        <v>2.41</v>
+        <v>2.97</v>
       </c>
       <c r="AD3">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AG3">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK3">
         <v>1.2</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4">
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.69</v>
+        <v>2.63</v>
       </c>
       <c r="O4">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="R4">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T4">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="U4">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="V4">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
         <v>1.11</v>
@@ -994,31 +994,31 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z4">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA4">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC4">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AD4">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE4">
         <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="AK4">
-        <v>2.07</v>
+        <v>1.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,65 +1124,65 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q5">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="R5">
+        <v>2.3</v>
+      </c>
+      <c r="S5">
+        <v>1.29</v>
+      </c>
+      <c r="T5">
+        <v>3.12</v>
+      </c>
+      <c r="U5">
+        <v>2.38</v>
+      </c>
+      <c r="V5">
+        <v>1.53</v>
+      </c>
+      <c r="W5">
+        <v>1.11</v>
+      </c>
+      <c r="X5">
+        <v>1.01</v>
+      </c>
+      <c r="Y5">
+        <v>1.2</v>
+      </c>
+      <c r="Z5">
+        <v>4.5</v>
+      </c>
+      <c r="AA5">
+        <v>1.65</v>
+      </c>
+      <c r="AB5">
+        <v>2.2</v>
+      </c>
+      <c r="AC5">
+        <v>2.63</v>
+      </c>
+      <c r="AD5">
+        <v>1.45</v>
+      </c>
+      <c r="AE5">
+        <v>1.14</v>
+      </c>
+      <c r="AF5">
+        <v>1.64</v>
+      </c>
+      <c r="AG5">
         <v>2.15</v>
       </c>
-      <c r="S5">
-        <v>1.31</v>
-      </c>
-      <c r="T5">
-        <v>2.94</v>
-      </c>
-      <c r="U5">
-        <v>2.51</v>
-      </c>
-      <c r="V5">
-        <v>1.42</v>
-      </c>
-      <c r="W5">
-        <v>1.09</v>
-      </c>
-      <c r="X5">
-        <v>1.03</v>
-      </c>
-      <c r="Y5">
-        <v>1.21</v>
-      </c>
-      <c r="Z5">
-        <v>3.58</v>
-      </c>
-      <c r="AA5">
-        <v>1.8</v>
-      </c>
-      <c r="AB5">
-        <v>1.95</v>
-      </c>
-      <c r="AC5">
-        <v>2.81</v>
-      </c>
-      <c r="AD5">
-        <v>1.39</v>
-      </c>
-      <c r="AE5">
-        <v>1.1</v>
-      </c>
-      <c r="AF5">
-        <v>1.59</v>
-      </c>
-      <c r="AG5">
-        <v>2.17</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>1.39</v>
+        <v>2.05</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
+        <v>2.45</v>
+      </c>
+      <c r="O6">
+        <v>3.1</v>
+      </c>
+      <c r="P6">
         <v>2.6</v>
       </c>
-      <c r="O6">
-        <v>3.2</v>
-      </c>
-      <c r="P6">
-        <v>2.42</v>
-      </c>
       <c r="Q6">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="R6">
         <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U6">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AA6">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB6">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AC6">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G4">
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.63</v>
+        <v>1.61</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P4">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q4">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T4">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="U4">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W4">
         <v>1.11</v>
@@ -994,31 +994,31 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA4">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB4">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC4">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AD4">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
         <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AG4">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="AK4">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.61</v>
+        <v>2.63</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q5">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="R5">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S5">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="V5">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
         <v>1.11</v>
@@ -1157,31 +1157,31 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA5">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC5">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AD5">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AE5">
         <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="AK5">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU7"/>
+  <dimension ref="A1:AU8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,12 +588,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G2">
@@ -631,68 +631,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:00:00</t>
+          <t>2026-09-24 12:00:00</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P3">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q3">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S3">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T3">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="U3">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA3">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB3">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC3">
-        <v>2.97</v>
+        <v>2.74</v>
       </c>
       <c r="AD3">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF3">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG3">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK3">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.61</v>
+        <v>3.85</v>
       </c>
       <c r="O4">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P4">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q4">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="R4">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T4">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="U4">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="V4">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
+        <v>1.25</v>
+      </c>
+      <c r="Z4">
+        <v>3.58</v>
+      </c>
+      <c r="AA4">
+        <v>1.87</v>
+      </c>
+      <c r="AB4">
+        <v>1.9</v>
+      </c>
+      <c r="AC4">
+        <v>2.97</v>
+      </c>
+      <c r="AD4">
+        <v>1.3</v>
+      </c>
+      <c r="AE4">
+        <v>1.07</v>
+      </c>
+      <c r="AF4">
+        <v>1.72</v>
+      </c>
+      <c r="AG4">
+        <v>1.93</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <v>1.19</v>
+      </c>
+      <c r="AK4">
         <v>1.2</v>
-      </c>
-      <c r="Z4">
-        <v>4.5</v>
-      </c>
-      <c r="AA4">
-        <v>1.65</v>
-      </c>
-      <c r="AB4">
-        <v>2.2</v>
-      </c>
-      <c r="AC4">
-        <v>2.63</v>
-      </c>
-      <c r="AD4">
-        <v>1.45</v>
-      </c>
-      <c r="AE4">
-        <v>1.14</v>
-      </c>
-      <c r="AF4">
-        <v>1.64</v>
-      </c>
-      <c r="AG4">
-        <v>2.15</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.16</v>
-      </c>
-      <c r="AK4">
-        <v>2.05</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,61 +1287,61 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.45</v>
+        <v>1.61</v>
       </c>
       <c r="O6">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P6">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q6">
-        <v>3.24</v>
+        <v>2.1</v>
       </c>
       <c r="R6">
+        <v>2.3</v>
+      </c>
+      <c r="S6">
+        <v>1.29</v>
+      </c>
+      <c r="T6">
+        <v>3.12</v>
+      </c>
+      <c r="U6">
+        <v>2.38</v>
+      </c>
+      <c r="V6">
+        <v>1.53</v>
+      </c>
+      <c r="W6">
+        <v>1.11</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>1.2</v>
+      </c>
+      <c r="Z6">
+        <v>4.5</v>
+      </c>
+      <c r="AA6">
+        <v>1.65</v>
+      </c>
+      <c r="AB6">
         <v>2.2</v>
       </c>
-      <c r="S6">
-        <v>1.3</v>
-      </c>
-      <c r="T6">
-        <v>3</v>
-      </c>
-      <c r="U6">
-        <v>2.48</v>
-      </c>
-      <c r="V6">
-        <v>1.43</v>
-      </c>
-      <c r="W6">
-        <v>1.1</v>
-      </c>
-      <c r="X6">
-        <v>1</v>
-      </c>
-      <c r="Y6">
-        <v>1.25</v>
-      </c>
-      <c r="Z6">
-        <v>3.6</v>
-      </c>
-      <c r="AA6">
-        <v>1.79</v>
-      </c>
-      <c r="AB6">
-        <v>1.88</v>
-      </c>
       <c r="AC6">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AD6">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AE6">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG6">
         <v>2.15</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK6">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-24 15:45:00</t>
+          <t>2026-09-24 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,156 +1403,319 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N7">
+        <v>2.45</v>
+      </c>
+      <c r="O7">
+        <v>3.1</v>
+      </c>
+      <c r="P7">
+        <v>2.6</v>
+      </c>
+      <c r="Q7">
+        <v>3.24</v>
+      </c>
+      <c r="R7">
+        <v>2.2</v>
+      </c>
+      <c r="S7">
+        <v>1.3</v>
+      </c>
+      <c r="T7">
+        <v>3</v>
+      </c>
+      <c r="U7">
+        <v>2.48</v>
+      </c>
+      <c r="V7">
+        <v>1.43</v>
+      </c>
+      <c r="W7">
+        <v>1.1</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1.25</v>
+      </c>
+      <c r="Z7">
+        <v>3.6</v>
+      </c>
+      <c r="AA7">
+        <v>1.79</v>
+      </c>
+      <c r="AB7">
+        <v>1.88</v>
+      </c>
+      <c r="AC7">
+        <v>2.88</v>
+      </c>
+      <c r="AD7">
+        <v>1.32</v>
+      </c>
+      <c r="AE7">
+        <v>1.12</v>
+      </c>
+      <c r="AF7">
+        <v>1.62</v>
+      </c>
+      <c r="AG7">
+        <v>2.15</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.24</v>
+      </c>
+      <c r="AK7">
+        <v>1.4</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>-1</v>
+      </c>
+      <c r="AN7">
+        <v>-1</v>
+      </c>
+      <c r="AO7">
+        <v>-1</v>
+      </c>
+      <c r="AP7">
+        <v>-1</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Morocco Botola Pro</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Amal Tiznit</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Ittihad Tanger</t>
         </is>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N7">
-        <v>2.75</v>
-      </c>
-      <c r="O7">
-        <v>2.5</v>
-      </c>
-      <c r="P7">
-        <v>2.45</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
+      <c r="N8">
+        <v>3.14</v>
+      </c>
+      <c r="O8">
+        <v>2.9</v>
+      </c>
+      <c r="P8">
+        <v>2.41</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
         <v>2.87</v>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <v>1.4</v>
       </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>-1</v>
-      </c>
-      <c r="AN7">
-        <v>-1</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>-1</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-1</v>
+      </c>
+      <c r="AN8">
+        <v>-1</v>
+      </c>
+      <c r="AO8">
+        <v>-1</v>
+      </c>
+      <c r="AP8">
+        <v>-1</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>2026-09-24 17:00:00</t>
         </is>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -798,52 +798,52 @@
         </is>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O3">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P3">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Q3">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="R3">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="S3">
         <v>1.28</v>
       </c>
       <c r="T3">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V3">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
         <v>1.1</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3">
         <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="AA3">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB3">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC3">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD3">
         <v>1.4</v>
@@ -852,10 +852,10 @@
         <v>1.13</v>
       </c>
       <c r="AF3">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG3">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK3">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="O4">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P4">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q4">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="R4">
         <v>2.2</v>
       </c>
       <c r="S4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T4">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="U4">
         <v>2.6</v>
@@ -988,10 +988,10 @@
         <v>1.39</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
         <v>1.25</v>
@@ -1000,10 +1000,10 @@
         <v>3.58</v>
       </c>
       <c r="AA4">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
         <v>2.97</v>
@@ -1015,10 +1015,10 @@
         <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG4">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
         <v>1.2</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="O5">
+        <v>3.32</v>
+      </c>
+      <c r="P5">
+        <v>2.33</v>
+      </c>
+      <c r="Q5">
         <v>3.3</v>
       </c>
-      <c r="P5">
-        <v>2.4</v>
-      </c>
-      <c r="Q5">
-        <v>3.15</v>
-      </c>
       <c r="R5">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
         <v>1.31</v>
@@ -1172,7 +1172,7 @@
         <v>2.88</v>
       </c>
       <c r="AD5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE5">
         <v>1.14</v>
@@ -1181,7 +1181,7 @@
         <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AK5">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,37 +1287,37 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="O6">
         <v>3.8</v>
       </c>
       <c r="P6">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q6">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R6">
         <v>2.3</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
         <v>3.12</v>
       </c>
       <c r="U6">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
         <v>1.2</v>
@@ -1326,7 +1326,7 @@
         <v>4.5</v>
       </c>
       <c r="AA6">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB6">
         <v>2.2</v>
@@ -1335,16 +1335,16 @@
         <v>2.63</v>
       </c>
       <c r="AD6">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE6">
         <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK6">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O7">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P7">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q7">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
       <c r="R7">
         <v>2.2</v>
@@ -1477,10 +1477,10 @@
         <v>1.43</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
         <v>1.25</v>
@@ -1495,7 +1495,7 @@
         <v>1.88</v>
       </c>
       <c r="AC7">
-        <v>2.88</v>
+        <v>3.16</v>
       </c>
       <c r="AD7">
         <v>1.32</v>
@@ -1504,10 +1504,10 @@
         <v>1.12</v>
       </c>
       <c r="AF7">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG7">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU8"/>
+  <dimension ref="A1:AU7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,12 +588,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G2">
@@ -631,68 +631,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-09-24 12:00:00</t>
+          <t>2026-09-24 13:00:00</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="O3">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P3">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="Q3">
-        <v>5.15</v>
+        <v>4.3</v>
       </c>
       <c r="R3">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="U3">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
+        <v>1.25</v>
+      </c>
+      <c r="Z3">
+        <v>3.58</v>
+      </c>
+      <c r="AA3">
+        <v>1.8</v>
+      </c>
+      <c r="AB3">
+        <v>1.95</v>
+      </c>
+      <c r="AC3">
+        <v>2.97</v>
+      </c>
+      <c r="AD3">
+        <v>1.3</v>
+      </c>
+      <c r="AE3">
+        <v>1.07</v>
+      </c>
+      <c r="AF3">
+        <v>1.68</v>
+      </c>
+      <c r="AG3">
+        <v>1.99</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
         <v>1.2</v>
       </c>
-      <c r="Z3">
-        <v>3.72</v>
-      </c>
-      <c r="AA3">
-        <v>1.73</v>
-      </c>
-      <c r="AB3">
-        <v>2</v>
-      </c>
-      <c r="AC3">
-        <v>2.7</v>
-      </c>
-      <c r="AD3">
-        <v>1.4</v>
-      </c>
-      <c r="AE3">
-        <v>1.13</v>
-      </c>
-      <c r="AF3">
-        <v>1.76</v>
-      </c>
-      <c r="AG3">
-        <v>1.88</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.16</v>
-      </c>
       <c r="AK3">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.7</v>
+        <v>1.73</v>
       </c>
       <c r="O4">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P4">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q4">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
+        <v>2.3</v>
+      </c>
+      <c r="S4">
+        <v>1.28</v>
+      </c>
+      <c r="T4">
+        <v>3.12</v>
+      </c>
+      <c r="U4">
+        <v>2.4</v>
+      </c>
+      <c r="V4">
+        <v>1.5</v>
+      </c>
+      <c r="W4">
+        <v>1.12</v>
+      </c>
+      <c r="X4">
+        <v>1.03</v>
+      </c>
+      <c r="Y4">
+        <v>1.2</v>
+      </c>
+      <c r="Z4">
+        <v>4.5</v>
+      </c>
+      <c r="AA4">
+        <v>1.6</v>
+      </c>
+      <c r="AB4">
         <v>2.2</v>
       </c>
-      <c r="S4">
-        <v>1.31</v>
-      </c>
-      <c r="T4">
-        <v>2.94</v>
-      </c>
-      <c r="U4">
-        <v>2.6</v>
-      </c>
-      <c r="V4">
-        <v>1.39</v>
-      </c>
-      <c r="W4">
-        <v>1.08</v>
-      </c>
-      <c r="X4">
-        <v>1.04</v>
-      </c>
-      <c r="Y4">
-        <v>1.25</v>
-      </c>
-      <c r="Z4">
-        <v>3.58</v>
-      </c>
-      <c r="AA4">
-        <v>1.8</v>
-      </c>
-      <c r="AB4">
-        <v>1.95</v>
-      </c>
       <c r="AC4">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="AD4">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE4">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AG4">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK4">
-        <v>1.2</v>
+        <v>1.91</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,65 +1287,65 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="O6">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q6">
-        <v>2.3</v>
+        <v>3.16</v>
       </c>
       <c r="R6">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
+        <v>1.08</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>1.25</v>
+      </c>
+      <c r="Z6">
+        <v>3.6</v>
+      </c>
+      <c r="AA6">
+        <v>1.79</v>
+      </c>
+      <c r="AB6">
+        <v>1.88</v>
+      </c>
+      <c r="AC6">
+        <v>3.16</v>
+      </c>
+      <c r="AD6">
+        <v>1.32</v>
+      </c>
+      <c r="AE6">
         <v>1.12</v>
       </c>
-      <c r="X6">
-        <v>1.03</v>
-      </c>
-      <c r="Y6">
-        <v>1.2</v>
-      </c>
-      <c r="Z6">
-        <v>4.5</v>
-      </c>
-      <c r="AA6">
+      <c r="AF6">
         <v>1.6</v>
       </c>
-      <c r="AB6">
+      <c r="AG6">
         <v>2.2</v>
       </c>
-      <c r="AC6">
-        <v>2.63</v>
-      </c>
-      <c r="AD6">
-        <v>1.44</v>
-      </c>
-      <c r="AE6">
-        <v>1.14</v>
-      </c>
-      <c r="AF6">
-        <v>1.59</v>
-      </c>
-      <c r="AG6">
-        <v>2.17</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK6">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-24 13:00:00</t>
+          <t>2026-09-24 15:45:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Amal Tiznit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="P7">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q7">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>1.79</v>
+        <v>3.1</v>
       </c>
       <c r="AB7">
-        <v>1.88</v>
+        <v>1.36</v>
       </c>
       <c r="AC7">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1553,169 +1553,6 @@
         <v>0</v>
       </c>
       <c r="AU7" t="inlineStr">
-        <is>
-          <t>2026-09-24 15:45:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Morocco Botola Pro</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Amal Tiznit</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Ittihad Tanger</t>
-        </is>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N8">
-        <v>3.14</v>
-      </c>
-      <c r="O8">
-        <v>2.9</v>
-      </c>
-      <c r="P8">
-        <v>2.41</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>2.87</v>
-      </c>
-      <c r="AB8">
-        <v>1.4</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>0</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>-1</v>
-      </c>
-      <c r="AN8">
-        <v>-1</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>-1</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
         <is>
           <t>2026-09-24 17:00:00</t>
         </is>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU7"/>
+  <dimension ref="A1:AU8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,12 +588,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G2">
@@ -631,68 +631,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:00:00</t>
+          <t>2026-09-24 12:00:00</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
+        <v>4.4</v>
+      </c>
+      <c r="O3">
         <v>3.7</v>
       </c>
-      <c r="O3">
-        <v>3.65</v>
-      </c>
       <c r="P3">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="Q3">
-        <v>4.3</v>
+        <v>5.15</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="S3">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T3">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="U3">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
+        <v>1.1</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3">
+        <v>1.2</v>
+      </c>
+      <c r="Z3">
+        <v>3.72</v>
+      </c>
+      <c r="AA3">
+        <v>1.73</v>
+      </c>
+      <c r="AB3">
+        <v>2</v>
+      </c>
+      <c r="AC3">
+        <v>2.7</v>
+      </c>
+      <c r="AD3">
+        <v>1.4</v>
+      </c>
+      <c r="AE3">
+        <v>1.13</v>
+      </c>
+      <c r="AF3">
+        <v>1.76</v>
+      </c>
+      <c r="AG3">
+        <v>1.88</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <v>1.16</v>
+      </c>
+      <c r="AK3">
         <v>1.08</v>
-      </c>
-      <c r="X3">
-        <v>1.04</v>
-      </c>
-      <c r="Y3">
-        <v>1.25</v>
-      </c>
-      <c r="Z3">
-        <v>3.58</v>
-      </c>
-      <c r="AA3">
-        <v>1.8</v>
-      </c>
-      <c r="AB3">
-        <v>1.95</v>
-      </c>
-      <c r="AC3">
-        <v>2.97</v>
-      </c>
-      <c r="AD3">
-        <v>1.3</v>
-      </c>
-      <c r="AE3">
-        <v>1.07</v>
-      </c>
-      <c r="AF3">
-        <v>1.68</v>
-      </c>
-      <c r="AG3">
-        <v>1.99</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.2</v>
-      </c>
-      <c r="AK3">
-        <v>1.2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.73</v>
+        <v>3.7</v>
       </c>
       <c r="O4">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P4">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="R4">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T4">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="U4">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V4">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W4">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
+        <v>1.25</v>
+      </c>
+      <c r="Z4">
+        <v>3.58</v>
+      </c>
+      <c r="AA4">
+        <v>1.8</v>
+      </c>
+      <c r="AB4">
+        <v>1.95</v>
+      </c>
+      <c r="AC4">
+        <v>2.97</v>
+      </c>
+      <c r="AD4">
+        <v>1.3</v>
+      </c>
+      <c r="AE4">
+        <v>1.07</v>
+      </c>
+      <c r="AF4">
+        <v>1.68</v>
+      </c>
+      <c r="AG4">
+        <v>1.99</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.2</v>
       </c>
-      <c r="Z4">
-        <v>4.5</v>
-      </c>
-      <c r="AA4">
-        <v>1.6</v>
-      </c>
-      <c r="AB4">
-        <v>2.2</v>
-      </c>
-      <c r="AC4">
-        <v>2.63</v>
-      </c>
-      <c r="AD4">
-        <v>1.44</v>
-      </c>
-      <c r="AE4">
-        <v>1.14</v>
-      </c>
-      <c r="AF4">
-        <v>1.59</v>
-      </c>
-      <c r="AG4">
-        <v>2.17</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.18</v>
-      </c>
       <c r="AK4">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
+        <v>1.73</v>
+      </c>
+      <c r="O6">
+        <v>3.8</v>
+      </c>
+      <c r="P6">
+        <v>3.8</v>
+      </c>
+      <c r="Q6">
+        <v>2.3</v>
+      </c>
+      <c r="R6">
+        <v>2.3</v>
+      </c>
+      <c r="S6">
+        <v>1.28</v>
+      </c>
+      <c r="T6">
+        <v>3.12</v>
+      </c>
+      <c r="U6">
         <v>2.4</v>
       </c>
-      <c r="O6">
-        <v>3.15</v>
-      </c>
-      <c r="P6">
-        <v>2.5</v>
-      </c>
-      <c r="Q6">
-        <v>3.16</v>
-      </c>
-      <c r="R6">
+      <c r="V6">
+        <v>1.5</v>
+      </c>
+      <c r="W6">
+        <v>1.12</v>
+      </c>
+      <c r="X6">
+        <v>1.03</v>
+      </c>
+      <c r="Y6">
+        <v>1.2</v>
+      </c>
+      <c r="Z6">
+        <v>4.5</v>
+      </c>
+      <c r="AA6">
+        <v>1.6</v>
+      </c>
+      <c r="AB6">
         <v>2.2</v>
       </c>
-      <c r="S6">
-        <v>1.3</v>
-      </c>
-      <c r="T6">
-        <v>3</v>
-      </c>
-      <c r="U6">
-        <v>2.48</v>
-      </c>
-      <c r="V6">
-        <v>1.43</v>
-      </c>
-      <c r="W6">
-        <v>1.08</v>
-      </c>
-      <c r="X6">
-        <v>1.01</v>
-      </c>
-      <c r="Y6">
-        <v>1.25</v>
-      </c>
-      <c r="Z6">
-        <v>3.6</v>
-      </c>
-      <c r="AA6">
-        <v>1.79</v>
-      </c>
-      <c r="AB6">
-        <v>1.88</v>
-      </c>
       <c r="AC6">
-        <v>3.16</v>
+        <v>2.63</v>
       </c>
       <c r="AD6">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE6">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG6">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK6">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-24 15:45:00</t>
+          <t>2026-09-24 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,156 +1403,319 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N7">
+        <v>2.4</v>
+      </c>
+      <c r="O7">
+        <v>3.15</v>
+      </c>
+      <c r="P7">
+        <v>2.5</v>
+      </c>
+      <c r="Q7">
+        <v>3.16</v>
+      </c>
+      <c r="R7">
+        <v>2.2</v>
+      </c>
+      <c r="S7">
+        <v>1.3</v>
+      </c>
+      <c r="T7">
+        <v>3</v>
+      </c>
+      <c r="U7">
+        <v>2.48</v>
+      </c>
+      <c r="V7">
+        <v>1.43</v>
+      </c>
+      <c r="W7">
+        <v>1.08</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>1.25</v>
+      </c>
+      <c r="Z7">
+        <v>3.6</v>
+      </c>
+      <c r="AA7">
+        <v>1.79</v>
+      </c>
+      <c r="AB7">
+        <v>1.88</v>
+      </c>
+      <c r="AC7">
+        <v>3.16</v>
+      </c>
+      <c r="AD7">
+        <v>1.32</v>
+      </c>
+      <c r="AE7">
+        <v>1.12</v>
+      </c>
+      <c r="AF7">
+        <v>1.6</v>
+      </c>
+      <c r="AG7">
+        <v>2.2</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.24</v>
+      </c>
+      <c r="AK7">
+        <v>1.4</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>-1</v>
+      </c>
+      <c r="AN7">
+        <v>-1</v>
+      </c>
+      <c r="AO7">
+        <v>-1</v>
+      </c>
+      <c r="AP7">
+        <v>-1</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Morocco Botola Pro</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Amal Tiznit</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Ittihad Tanger</t>
         </is>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N7">
-        <v>3.2</v>
-      </c>
-      <c r="O7">
-        <v>2.9</v>
-      </c>
-      <c r="P7">
-        <v>2.37</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
+      <c r="N8">
+        <v>2.96</v>
+      </c>
+      <c r="O8">
+        <v>2.7</v>
+      </c>
+      <c r="P8">
+        <v>2.35</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
         <v>3.1</v>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <v>1.36</v>
       </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>-1</v>
-      </c>
-      <c r="AN7">
-        <v>-1</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>-1</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-1</v>
+      </c>
+      <c r="AN8">
+        <v>-1</v>
+      </c>
+      <c r="AO8">
+        <v>-1</v>
+      </c>
+      <c r="AP8">
+        <v>-1</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>2026-09-24 17:00:00</t>
         </is>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="O5">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>2.33</v>
+        <v>3.8</v>
       </c>
       <c r="Q5">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="R5">
+        <v>2.3</v>
+      </c>
+      <c r="S5">
+        <v>1.28</v>
+      </c>
+      <c r="T5">
+        <v>3.12</v>
+      </c>
+      <c r="U5">
+        <v>2.4</v>
+      </c>
+      <c r="V5">
+        <v>1.5</v>
+      </c>
+      <c r="W5">
+        <v>1.12</v>
+      </c>
+      <c r="X5">
+        <v>1.03</v>
+      </c>
+      <c r="Y5">
+        <v>1.2</v>
+      </c>
+      <c r="Z5">
+        <v>4.5</v>
+      </c>
+      <c r="AA5">
+        <v>1.6</v>
+      </c>
+      <c r="AB5">
         <v>2.2</v>
       </c>
-      <c r="S5">
-        <v>1.31</v>
-      </c>
-      <c r="T5">
-        <v>2.94</v>
-      </c>
-      <c r="U5">
-        <v>2.51</v>
-      </c>
-      <c r="V5">
+      <c r="AC5">
+        <v>2.63</v>
+      </c>
+      <c r="AD5">
         <v>1.44</v>
-      </c>
-      <c r="W5">
-        <v>1.11</v>
-      </c>
-      <c r="X5">
-        <v>1.01</v>
-      </c>
-      <c r="Y5">
-        <v>1.21</v>
-      </c>
-      <c r="Z5">
-        <v>4.2</v>
-      </c>
-      <c r="AA5">
-        <v>1.8</v>
-      </c>
-      <c r="AB5">
-        <v>2</v>
-      </c>
-      <c r="AC5">
-        <v>2.88</v>
-      </c>
-      <c r="AD5">
-        <v>1.34</v>
       </c>
       <c r="AE5">
         <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG5">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
-        <v>3.8</v>
+        <v>3.32</v>
       </c>
       <c r="P6">
-        <v>3.8</v>
+        <v>2.33</v>
       </c>
       <c r="Q6">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T6">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA6">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AB6">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC6">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AD6">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AE6">
         <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AK6">
-        <v>1.91</v>
+        <v>1.38</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.96</v>
+        <v>2.45</v>
       </c>
       <c r="O8">
         <v>2.7</v>
       </c>
       <c r="P8">
-        <v>2.35</v>
+        <v>2.93</v>
       </c>
       <c r="Q8">
         <v>0</v>

--- a/jogos_2026-09-24.xlsx
+++ b/jogos_2026-09-24.xlsx
@@ -775,130 +775,130 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>4.4</v>
+        <v>6.07</v>
       </c>
       <c r="O3">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="P3">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="Q3">
-        <v>5.15</v>
+        <v>6.2</v>
       </c>
       <c r="R3">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="S3">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U3">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z3">
-        <v>3.72</v>
+        <v>4.15</v>
       </c>
       <c r="AA3">
+        <v>1.47</v>
+      </c>
+      <c r="AB3">
+        <v>2.15</v>
+      </c>
+      <c r="AC3">
+        <v>2.43</v>
+      </c>
+      <c r="AD3">
+        <v>1.44</v>
+      </c>
+      <c r="AE3">
+        <v>1.15</v>
+      </c>
+      <c r="AF3">
+        <v>1.62</v>
+      </c>
+      <c r="AG3">
         <v>1.73</v>
       </c>
-      <c r="AB3">
-        <v>2</v>
-      </c>
-      <c r="AC3">
-        <v>2.7</v>
-      </c>
-      <c r="AD3">
-        <v>1.4</v>
-      </c>
-      <c r="AE3">
-        <v>1.13</v>
-      </c>
-      <c r="AF3">
-        <v>1.76</v>
-      </c>
-      <c r="AG3">
-        <v>1.88</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "49", "55"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AK3">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -941,84 +941,84 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="O4">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="Q4">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="R4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T4">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="U4">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V4">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="AA4">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB4">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC4">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AD4">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG4">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1027,41 +1027,41 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "47", "81"]</t>
         </is>
       </c>
       <c r="AJ4">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK4">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1113,118 +1113,118 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P5">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="S5">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T5">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U5">
+        <v>2.2</v>
+      </c>
+      <c r="V5">
+        <v>1.6</v>
+      </c>
+      <c r="W5">
+        <v>1.15</v>
+      </c>
+      <c r="X5">
+        <v>1.01</v>
+      </c>
+      <c r="Y5">
+        <v>1.13</v>
+      </c>
+      <c r="Z5">
+        <v>5.2</v>
+      </c>
+      <c r="AA5">
+        <v>1.57</v>
+      </c>
+      <c r="AB5">
+        <v>2.25</v>
+      </c>
+      <c r="AC5">
         <v>2.4</v>
       </c>
-      <c r="V5">
-        <v>1.5</v>
-      </c>
-      <c r="W5">
-        <v>1.12</v>
-      </c>
-      <c r="X5">
-        <v>1.03</v>
-      </c>
-      <c r="Y5">
-        <v>1.2</v>
-      </c>
-      <c r="Z5">
-        <v>4.5</v>
-      </c>
-      <c r="AA5">
-        <v>1.6</v>
-      </c>
-      <c r="AB5">
-        <v>2.2</v>
-      </c>
-      <c r="AC5">
-        <v>2.63</v>
-      </c>
       <c r="AD5">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF5">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AG5">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
+          <t>["84"]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ5">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AK5">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,130 +1264,130 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
         <v>2.6</v>
       </c>
       <c r="O6">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
         <v>2.33</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S6">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="U6">
-        <v>2.51</v>
+        <v>2.06</v>
       </c>
       <c r="V6">
         <v>1.44</v>
       </c>
       <c r="W6">
+        <v>1.06</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1.19</v>
+      </c>
+      <c r="Z6">
+        <v>3</v>
+      </c>
+      <c r="AA6">
+        <v>1.72</v>
+      </c>
+      <c r="AB6">
+        <v>1.79</v>
+      </c>
+      <c r="AC6">
+        <v>2.3</v>
+      </c>
+      <c r="AD6">
+        <v>1.36</v>
+      </c>
+      <c r="AE6">
         <v>1.11</v>
       </c>
-      <c r="X6">
-        <v>1.01</v>
-      </c>
-      <c r="Y6">
-        <v>1.21</v>
-      </c>
-      <c r="Z6">
-        <v>4.2</v>
-      </c>
-      <c r="AA6">
-        <v>1.8</v>
-      </c>
-      <c r="AB6">
-        <v>2</v>
-      </c>
-      <c r="AC6">
-        <v>2.88</v>
-      </c>
-      <c r="AD6">
-        <v>1.34</v>
-      </c>
-      <c r="AE6">
-        <v>1.14</v>
-      </c>
       <c r="AF6">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG6">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "66", "69"]</t>
         </is>
       </c>
       <c r="AJ6">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AK6">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1450,37 +1450,37 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="O7">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q7">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
         <v>3</v>
       </c>
       <c r="U7">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
         <v>1.25</v>
@@ -1489,25 +1489,25 @@
         <v>3.6</v>
       </c>
       <c r="AA7">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB7">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC7">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="AD7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
         <v>1.12</v>
       </c>
       <c r="AF7">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG7">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL7">
         <v>0</v>
